--- a/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
+++ b/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GREEN ENERBRAS ONE SCSp\GREEN ENERBRAS ONE SCSp\BILAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF218B0E-0D1E-4DF2-9141-0DDC0F07B993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ABADEB-2435-45DE-B8D7-AD2B5B979928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7107,16 +7107,15 @@
         <v>-341.88</v>
       </c>
       <c r="P42" s="27">
-        <f>O42*$P$5</f>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="Q42" s="27">
         <f>O42+P42</f>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="R42" s="35">
         <f t="shared" si="12"/>
-        <v>49573.517400000004</v>
+        <v>49573.517000000007</v>
       </c>
       <c r="U42" s="36"/>
     </row>
@@ -7167,16 +7166,15 @@
         <v>-341.88</v>
       </c>
       <c r="P43" s="27">
-        <f t="shared" ref="P43:P52" si="22">O43*$P$5</f>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="Q43" s="27">
-        <f t="shared" ref="Q43:Q47" si="23">O43+P43</f>
-        <v>-399.99959999999999</v>
+        <f t="shared" ref="Q43:Q47" si="22">O43+P43</f>
+        <v>-400</v>
       </c>
       <c r="R43" s="35">
         <f t="shared" si="12"/>
-        <v>49173.517800000001</v>
+        <v>49173.517000000007</v>
       </c>
       <c r="U43" s="36"/>
     </row>
@@ -7227,16 +7225,15 @@
         <v>-341.88</v>
       </c>
       <c r="P44" s="27">
+        <v>-58.12</v>
+      </c>
+      <c r="Q44" s="27">
         <f t="shared" si="22"/>
-        <v>-58.119600000000005</v>
-      </c>
-      <c r="Q44" s="27">
-        <f t="shared" si="23"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="R44" s="35">
         <f t="shared" si="12"/>
-        <v>48773.518199999999</v>
+        <v>48773.517000000007</v>
       </c>
       <c r="U44" s="36"/>
     </row>
@@ -7287,16 +7284,15 @@
         <v>-341.88</v>
       </c>
       <c r="P45" s="27">
+        <v>-58.12</v>
+      </c>
+      <c r="Q45" s="27">
         <f t="shared" si="22"/>
-        <v>-58.119600000000005</v>
-      </c>
-      <c r="Q45" s="27">
-        <f t="shared" si="23"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="R45" s="35">
         <f t="shared" si="12"/>
-        <v>48373.518599999996</v>
+        <v>48373.517000000007</v>
       </c>
       <c r="U45" s="36"/>
     </row>
@@ -7347,16 +7343,15 @@
         <v>-341.88</v>
       </c>
       <c r="P46" s="27">
+        <v>-58.12</v>
+      </c>
+      <c r="Q46" s="27">
         <f t="shared" si="22"/>
-        <v>-58.119600000000005</v>
-      </c>
-      <c r="Q46" s="27">
-        <f t="shared" si="23"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="R46" s="35">
         <f t="shared" si="12"/>
-        <v>47973.518999999993</v>
+        <v>47973.517000000007</v>
       </c>
       <c r="U46" s="36"/>
     </row>
@@ -7408,16 +7403,15 @@
         <v>-683.76</v>
       </c>
       <c r="P47" s="27">
+        <v>-116.24</v>
+      </c>
+      <c r="Q47" s="27">
         <f t="shared" si="22"/>
-        <v>-116.23920000000001</v>
-      </c>
-      <c r="Q47" s="27">
-        <f t="shared" si="23"/>
-        <v>-799.99919999999997</v>
+        <v>-800</v>
       </c>
       <c r="R47" s="35">
         <f t="shared" si="12"/>
-        <v>47173.519799999995</v>
+        <v>47173.517000000007</v>
       </c>
       <c r="U47" s="36"/>
     </row>
@@ -7468,16 +7462,15 @@
         <v>-341.88</v>
       </c>
       <c r="P48" s="27">
-        <f t="shared" si="22"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="Q48" s="27">
-        <f t="shared" ref="Q48" si="24">O48+P48</f>
-        <v>-399.99959999999999</v>
+        <f t="shared" ref="Q48" si="23">O48+P48</f>
+        <v>-400</v>
       </c>
       <c r="R48" s="35">
         <f t="shared" si="12"/>
-        <v>46773.520199999992</v>
+        <v>46773.517000000007</v>
       </c>
       <c r="U48" s="36"/>
     </row>
@@ -7528,16 +7521,15 @@
         <v>-341.88</v>
       </c>
       <c r="P49" s="27">
-        <f t="shared" si="22"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="Q49" s="27">
-        <f t="shared" ref="Q49" si="25">O49+P49</f>
-        <v>-399.99959999999999</v>
+        <f t="shared" ref="Q49" si="24">O49+P49</f>
+        <v>-400</v>
       </c>
       <c r="R49" s="35">
         <f t="shared" si="12"/>
-        <v>46373.520599999989</v>
+        <v>46373.517000000007</v>
       </c>
       <c r="U49" s="36"/>
     </row>
@@ -7588,16 +7580,15 @@
         <v>-341.88</v>
       </c>
       <c r="P50" s="27">
-        <f t="shared" si="22"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="Q50" s="27">
-        <f t="shared" ref="Q50:Q54" si="26">O50+P50</f>
-        <v>-399.99959999999999</v>
+        <f t="shared" ref="Q50:Q54" si="25">O50+P50</f>
+        <v>-400</v>
       </c>
       <c r="R50" s="35">
         <f t="shared" si="12"/>
-        <v>45973.520999999986</v>
+        <v>45973.517000000007</v>
       </c>
       <c r="U50" s="36"/>
     </row>
@@ -7650,16 +7641,15 @@
         <v>3418.8</v>
       </c>
       <c r="P51" s="27">
-        <f>O51*$P$5</f>
-        <v>581.19600000000003</v>
+        <v>581.20000000000005</v>
       </c>
       <c r="Q51" s="27">
         <f>O51+P51</f>
-        <v>3999.9960000000001</v>
+        <v>4000</v>
       </c>
       <c r="R51" s="35">
         <f t="shared" si="12"/>
-        <v>49973.516999999985</v>
+        <v>49973.517000000007</v>
       </c>
       <c r="U51" s="36"/>
     </row>
@@ -7712,16 +7702,15 @@
         <v>-3418.8</v>
       </c>
       <c r="P52" s="27">
-        <f t="shared" si="22"/>
-        <v>-581.19600000000003</v>
+        <v>-581.20000000000005</v>
       </c>
       <c r="Q52" s="27">
-        <f t="shared" si="26"/>
-        <v>-3999.9960000000001</v>
+        <f t="shared" si="25"/>
+        <v>-4000</v>
       </c>
       <c r="R52" s="35">
         <f t="shared" si="12"/>
-        <v>45973.520999999986</v>
+        <v>45973.517000000007</v>
       </c>
       <c r="U52" s="36"/>
     </row>
@@ -7771,12 +7760,12 @@
         <v>0</v>
       </c>
       <c r="Q53" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-250</v>
       </c>
       <c r="R53" s="35">
         <f t="shared" si="12"/>
-        <v>45723.520999999986</v>
+        <v>45723.517000000007</v>
       </c>
       <c r="U53" s="36"/>
     </row>
@@ -7829,12 +7818,12 @@
         <v>-2.5500000000000003</v>
       </c>
       <c r="Q54" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-17.55</v>
       </c>
       <c r="R54" s="35">
         <f t="shared" si="12"/>
-        <v>45705.970999999983</v>
+        <v>45705.967000000004</v>
       </c>
       <c r="U54" s="36"/>
     </row>
@@ -7888,7 +7877,7 @@
       </c>
       <c r="R55" s="35">
         <f t="shared" si="12"/>
-        <v>45723.520999999986</v>
+        <v>45723.517000000007</v>
       </c>
       <c r="U55" s="36"/>
     </row>
@@ -7936,16 +7925,16 @@
         <v>-15</v>
       </c>
       <c r="P56" s="27">
-        <f t="shared" ref="P56:Q56" si="27">-P55</f>
+        <f t="shared" ref="P56:Q56" si="26">-P55</f>
         <v>-2.5499999999999998</v>
       </c>
       <c r="Q56" s="27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>-17.55</v>
       </c>
       <c r="R56" s="35">
         <f t="shared" si="12"/>
-        <v>45705.970999999983</v>
+        <v>45705.967000000004</v>
       </c>
       <c r="U56" s="36"/>
     </row>
@@ -7995,12 +7984,12 @@
         <v>0</v>
       </c>
       <c r="Q57" s="27">
-        <f t="shared" ref="Q57:Q61" si="28">O57+P57</f>
+        <f t="shared" ref="Q57:Q61" si="27">O57+P57</f>
         <v>-40000</v>
       </c>
       <c r="R57" s="35">
         <f t="shared" si="12"/>
-        <v>5705.9709999999832</v>
+        <v>5705.9670000000042</v>
       </c>
       <c r="U57" s="36"/>
     </row>
@@ -8050,12 +8039,12 @@
         <v>0</v>
       </c>
       <c r="Q58" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>-5</v>
       </c>
       <c r="R58" s="35">
         <f t="shared" si="12"/>
-        <v>5700.9709999999832</v>
+        <v>5700.9670000000042</v>
       </c>
       <c r="U58" s="36"/>
     </row>
@@ -8105,12 +8094,12 @@
         <v>0</v>
       </c>
       <c r="Q59" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>-4</v>
       </c>
       <c r="R59" s="35">
         <f t="shared" si="12"/>
-        <v>5696.9709999999832</v>
+        <v>5696.9670000000042</v>
       </c>
       <c r="U59" s="36"/>
     </row>
@@ -8162,12 +8151,12 @@
         <v>0</v>
       </c>
       <c r="Q60" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>40000</v>
       </c>
       <c r="R60" s="35">
         <f t="shared" si="12"/>
-        <v>45696.970999999983</v>
+        <v>45696.967000000004</v>
       </c>
       <c r="U60" s="36"/>
     </row>
@@ -8219,12 +8208,12 @@
         <v>0</v>
       </c>
       <c r="Q61" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>20000</v>
       </c>
       <c r="R61" s="35">
         <f t="shared" si="12"/>
-        <v>65696.97099999999</v>
+        <v>65696.967000000004</v>
       </c>
       <c r="U61" s="36"/>
     </row>
@@ -8240,11 +8229,11 @@
         <v>46220</v>
       </c>
       <c r="E62" s="9">
-        <f t="shared" ref="E62:E68" si="29">IF(C62="","",MONTH(C62))</f>
+        <f t="shared" ref="E62:E68" si="28">IF(C62="","",MONTH(C62))</f>
         <v>7</v>
       </c>
       <c r="F62" s="9">
-        <f t="shared" ref="F62:F68" si="30">IF(C62="","",YEAR(C62))</f>
+        <f t="shared" ref="F62:F68" si="29">IF(C62="","",YEAR(C62))</f>
         <v>2026</v>
       </c>
       <c r="G62" s="9">
@@ -8275,16 +8264,15 @@
         <v>-683.76</v>
       </c>
       <c r="P62" s="27">
-        <f t="shared" ref="P62:P63" si="31">O62*$P$5</f>
-        <v>-116.23920000000001</v>
+        <v>-116.24</v>
       </c>
       <c r="Q62" s="27">
-        <f t="shared" ref="Q62:Q63" si="32">O62+P62</f>
-        <v>-799.99919999999997</v>
+        <f t="shared" ref="Q62:Q63" si="30">O62+P62</f>
+        <v>-800</v>
       </c>
       <c r="R62" s="35">
         <f t="shared" si="12"/>
-        <v>64896.971799999992</v>
+        <v>64896.967000000004</v>
       </c>
       <c r="U62" s="36"/>
     </row>
@@ -8300,11 +8288,11 @@
         <v>46220</v>
       </c>
       <c r="E63" s="9">
+        <f t="shared" si="28"/>
+        <v>7</v>
+      </c>
+      <c r="F63" s="9">
         <f t="shared" si="29"/>
-        <v>7</v>
-      </c>
-      <c r="F63" s="9">
-        <f t="shared" si="30"/>
         <v>2026</v>
       </c>
       <c r="G63" s="9">
@@ -8335,16 +8323,15 @@
         <v>-341.88</v>
       </c>
       <c r="P63" s="27">
-        <f t="shared" si="31"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="Q63" s="27">
-        <f t="shared" si="32"/>
-        <v>-399.99959999999999</v>
+        <f t="shared" si="30"/>
+        <v>-400</v>
       </c>
       <c r="R63" s="35">
         <f t="shared" si="12"/>
-        <v>64496.972199999989</v>
+        <v>64496.967000000004</v>
       </c>
       <c r="U63" s="36"/>
     </row>
@@ -8360,11 +8347,11 @@
         <v>46220</v>
       </c>
       <c r="E64" s="9">
+        <f t="shared" si="28"/>
+        <v>7</v>
+      </c>
+      <c r="F64" s="9">
         <f t="shared" si="29"/>
-        <v>7</v>
-      </c>
-      <c r="F64" s="9">
-        <f t="shared" si="30"/>
         <v>2026</v>
       </c>
       <c r="G64" s="9">
@@ -8397,16 +8384,15 @@
         <v>1025.6399999999999</v>
       </c>
       <c r="P64" s="27">
-        <f>O64*$P$5</f>
-        <v>174.3588</v>
+        <v>174.36</v>
       </c>
       <c r="Q64" s="27">
         <f>O64+P64</f>
-        <v>1199.9987999999998</v>
+        <v>1200</v>
       </c>
       <c r="R64" s="35">
         <f t="shared" si="12"/>
-        <v>65696.97099999999</v>
+        <v>65696.967000000004</v>
       </c>
       <c r="U64" s="36"/>
     </row>
@@ -8422,11 +8408,11 @@
         <v>46220</v>
       </c>
       <c r="E65" s="9">
+        <f t="shared" si="28"/>
+        <v>7</v>
+      </c>
+      <c r="F65" s="9">
         <f t="shared" si="29"/>
-        <v>7</v>
-      </c>
-      <c r="F65" s="9">
-        <f t="shared" si="30"/>
         <v>2026</v>
       </c>
       <c r="G65" s="9">
@@ -8459,16 +8445,15 @@
         <v>-1025.6399999999999</v>
       </c>
       <c r="P65" s="27">
-        <f t="shared" ref="P65" si="33">O65*$P$5</f>
-        <v>-174.3588</v>
+        <v>-174.36</v>
       </c>
       <c r="Q65" s="27">
-        <f t="shared" ref="Q65:Q68" si="34">O65+P65</f>
-        <v>-1199.9987999999998</v>
+        <f t="shared" ref="Q65:Q68" si="31">O65+P65</f>
+        <v>-1200</v>
       </c>
       <c r="R65" s="35">
         <f t="shared" si="12"/>
-        <v>64496.972199999989</v>
+        <v>64496.967000000004</v>
       </c>
       <c r="U65" s="36"/>
     </row>
@@ -8484,11 +8469,11 @@
         <v>46224</v>
       </c>
       <c r="E66" s="9">
+        <f t="shared" si="28"/>
+        <v>7</v>
+      </c>
+      <c r="F66" s="9">
         <f t="shared" si="29"/>
-        <v>7</v>
-      </c>
-      <c r="F66" s="9">
-        <f t="shared" si="30"/>
         <v>2026</v>
       </c>
       <c r="G66" s="9">
@@ -8518,12 +8503,12 @@
         <v>0</v>
       </c>
       <c r="Q66" s="27">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>-250</v>
       </c>
       <c r="R66" s="35">
         <f t="shared" si="12"/>
-        <v>64246.972199999989</v>
+        <v>64246.967000000004</v>
       </c>
       <c r="U66" s="36"/>
     </row>
@@ -8539,11 +8524,11 @@
         <v>46230</v>
       </c>
       <c r="E67" s="9">
+        <f t="shared" si="28"/>
+        <v>7</v>
+      </c>
+      <c r="F67" s="9">
         <f t="shared" si="29"/>
-        <v>7</v>
-      </c>
-      <c r="F67" s="9">
-        <f t="shared" si="30"/>
         <v>2026</v>
       </c>
       <c r="G67" s="9">
@@ -8573,12 +8558,12 @@
         <v>0</v>
       </c>
       <c r="Q67" s="27">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>-50000</v>
       </c>
       <c r="R67" s="35">
         <f t="shared" si="12"/>
-        <v>14246.972199999989</v>
+        <v>14246.967000000004</v>
       </c>
       <c r="U67" s="36"/>
     </row>
@@ -8594,11 +8579,11 @@
         <v>46230</v>
       </c>
       <c r="E68" s="9">
+        <f t="shared" si="28"/>
+        <v>7</v>
+      </c>
+      <c r="F68" s="9">
         <f t="shared" si="29"/>
-        <v>7</v>
-      </c>
-      <c r="F68" s="9">
-        <f t="shared" si="30"/>
         <v>2026</v>
       </c>
       <c r="G68" s="9">
@@ -8628,12 +8613,12 @@
         <v>0</v>
       </c>
       <c r="Q68" s="27">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>-25</v>
       </c>
       <c r="R68" s="35">
         <f t="shared" si="12"/>
-        <v>14221.972199999989</v>
+        <v>14221.967000000004</v>
       </c>
       <c r="U68" s="36"/>
     </row>
@@ -8652,7 +8637,7 @@
       <c r="Q69" s="27"/>
       <c r="R69" s="35">
         <f t="shared" si="12"/>
-        <v>14221.972199999989</v>
+        <v>14221.967000000004</v>
       </c>
       <c r="U69" s="36"/>
     </row>
@@ -8672,7 +8657,7 @@
       <c r="Q70" s="27"/>
       <c r="R70" s="35">
         <f t="shared" si="12"/>
-        <v>14221.972199999989</v>
+        <v>14221.967000000004</v>
       </c>
       <c r="U70" s="36"/>
     </row>
@@ -8691,7 +8676,7 @@
       <c r="P71" s="27"/>
       <c r="Q71" s="27"/>
       <c r="R71" s="35" t="str">
-        <f t="shared" ref="R71" si="35">IF(Q71="",".",R70+Q71)</f>
+        <f t="shared" ref="R71" si="32">IF(Q71="",".",R70+Q71)</f>
         <v>.</v>
       </c>
       <c r="U71" s="36"/>
@@ -8716,15 +8701,15 @@
       </c>
       <c r="P72" s="40">
         <f>SUM(P7:P71)</f>
-        <v>-805.68779999999992</v>
+        <v>-805.69299999999998</v>
       </c>
       <c r="Q72" s="40">
         <f>SUM(Q7:Q71)</f>
-        <v>14221.972199999989</v>
+        <v>14221.967000000004</v>
       </c>
       <c r="R72" s="41">
         <f>INDEX(R7:R71,COUNTIF(R7:R71,"&lt;&gt;."))</f>
-        <v>14221.972199999989</v>
+        <v>14221.967000000004</v>
       </c>
       <c r="U72" s="36"/>
     </row>
@@ -8755,11 +8740,11 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="9" t="str">
-        <f t="shared" ref="E74:E76" si="36">IF(C74="","",MONTH(C74))</f>
+        <f t="shared" ref="E74:E76" si="33">IF(C74="","",MONTH(C74))</f>
         <v/>
       </c>
       <c r="F74" s="9" t="str">
-        <f t="shared" ref="F74:F76" si="37">IF(C74="","",YEAR(C74))</f>
+        <f t="shared" ref="F74:F76" si="34">IF(C74="","",YEAR(C74))</f>
         <v/>
       </c>
       <c r="G74" s="9"/>
@@ -8783,7 +8768,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="27">
-        <f t="shared" ref="Q74:Q76" si="38">O74+P74</f>
+        <f t="shared" ref="Q74:Q76" si="35">O74+P74</f>
         <v>0</v>
       </c>
       <c r="R74" s="35">
@@ -8800,11 +8785,11 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="F75" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="G75" s="9"/>
@@ -8829,11 +8814,11 @@
         <v>0</v>
       </c>
       <c r="P75" s="27">
-        <f t="shared" ref="P75:P76" si="39">O75*$P$5</f>
+        <f t="shared" ref="P75:P76" si="36">O75*$P$5</f>
         <v>0</v>
       </c>
       <c r="Q75" s="27">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R75" s="35">
@@ -8850,11 +8835,11 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="F76" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="G76" s="9"/>
@@ -8880,11 +8865,11 @@
         <v>0</v>
       </c>
       <c r="P76" s="27">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Q76" s="27">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R76" s="35">

--- a/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
+++ b/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GREEN ENERBRAS ONE SCSp\GREEN ENERBRAS ONE SCSp\BILAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ABADEB-2435-45DE-B8D7-AD2B5B979928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443AC865-550A-40D5-BAD4-7BF25EE532CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -737,9 +737,6 @@
     <t>NEW LIFE Sarl</t>
   </si>
   <si>
-    <t>New Life Sarl</t>
-  </si>
-  <si>
     <t>Frais d'extrait RCS - Papier Securise</t>
   </si>
   <si>
@@ -780,6 +777,9 @@
   </si>
   <si>
     <t>Cambio medio</t>
+  </si>
+  <si>
+    <t>New Life Sarl (General Partner)</t>
   </si>
 </sst>
 </file>
@@ -2324,7 +2324,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Utilisateur" refreshedDate="46231.360567013886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="67" xr:uid="{BEC7E0F4-8CE4-4ECA-8BD9-B963401BB7CD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Utilisateur" refreshedDate="46271.885039236113" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="67" xr:uid="{BEC7E0F4-8CE4-4ECA-8BD9-B963401BB7CD}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:Y68" sheet="COMPTAB"/>
   </cacheSource>
@@ -2350,22 +2350,22 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2025" maxValue="2026"/>
     </cacheField>
     <cacheField name="BRL" numFmtId="173">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1156585"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="227258" maxValue="1443941"/>
     </cacheField>
     <cacheField name="Change" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="6.3568199999999999"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="5.6814499999999999" maxValue="6.3568199999999999"/>
     </cacheField>
     <cacheField name="INTR" numFmtId="1">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Imp" numFmtId="8">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-50000" maxValue="40000"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-240000" maxValue="40000"/>
     </cacheField>
     <cacheField name="% TVA" numFmtId="10">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="0.17"/>
     </cacheField>
     <cacheField name="TVA" numFmtId="8">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-581.19600000000003" maxValue="581.19600000000003"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-581.20000000000005" maxValue="581.20000000000005"/>
     </cacheField>
     <cacheField name="Importo" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-50000" maxValue="40000"/>
@@ -3409,9 +3409,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="49573.517400000004"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="49573.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3436,9 +3436,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="49173.517800000001"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="49173.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3463,9 +3463,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="48773.518199999999"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="48773.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3490,9 +3490,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="48373.518599999996"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="48373.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3517,9 +3517,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="47973.518999999993"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="47973.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3544,9 +3544,9 @@
     <s v="LUX"/>
     <n v="-683.76"/>
     <n v="0.17"/>
-    <n v="-116.23920000000001"/>
-    <n v="-799.99919999999997"/>
-    <n v="47173.519799999995"/>
+    <n v="-116.24"/>
+    <n v="-800"/>
+    <n v="47173.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3571,9 +3571,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="46773.520199999992"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="46773.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3598,9 +3598,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="46373.520599999989"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="46373.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3625,9 +3625,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="45973.520999999986"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="45973.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3652,9 +3652,9 @@
     <s v="LUX"/>
     <n v="3418.8"/>
     <n v="0.17"/>
-    <n v="581.19600000000003"/>
-    <n v="3999.9960000000001"/>
-    <n v="49973.516999999985"/>
+    <n v="581.20000000000005"/>
+    <n v="4000"/>
+    <n v="49973.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3679,9 +3679,9 @@
     <s v="LUX"/>
     <n v="-3418.8"/>
     <n v="0.17"/>
-    <n v="-581.19600000000003"/>
-    <n v="-3999.9960000000001"/>
-    <n v="45973.520999999986"/>
+    <n v="-581.20000000000005"/>
+    <n v="-4000"/>
+    <n v="45973.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3708,7 +3708,7 @@
     <m/>
     <m/>
     <n v="-250"/>
-    <n v="45723.520999999986"/>
+    <n v="45723.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3735,7 +3735,7 @@
     <n v="0.17"/>
     <n v="-2.5500000000000003"/>
     <n v="-17.55"/>
-    <n v="45705.970999999983"/>
+    <n v="45705.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3762,7 +3762,7 @@
     <n v="0.17"/>
     <n v="2.5499999999999998"/>
     <n v="17.55"/>
-    <n v="45723.520999999986"/>
+    <n v="45723.517000000007"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3789,7 +3789,7 @@
     <n v="0.17"/>
     <n v="-2.5499999999999998"/>
     <n v="-17.55"/>
-    <n v="45705.970999999983"/>
+    <n v="45705.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3816,7 +3816,7 @@
     <m/>
     <m/>
     <n v="-40000"/>
-    <n v="5705.9709999999832"/>
+    <n v="5705.9670000000042"/>
     <x v="0"/>
     <x v="2"/>
     <s v="23 - IMMOBILISATIONS FINANCIERES"/>
@@ -3843,7 +3843,7 @@
     <m/>
     <m/>
     <n v="-5"/>
-    <n v="5700.9709999999832"/>
+    <n v="5700.9670000000042"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3870,7 +3870,7 @@
     <m/>
     <m/>
     <n v="-4"/>
-    <n v="5696.9709999999832"/>
+    <n v="5696.9670000000042"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3897,7 +3897,7 @@
     <m/>
     <m/>
     <n v="40000"/>
-    <n v="45696.970999999983"/>
+    <n v="45696.967000000004"/>
     <x v="0"/>
     <x v="0"/>
     <s v="A. CAPITAUX PROPRES"/>
@@ -3924,7 +3924,7 @@
     <m/>
     <m/>
     <n v="20000"/>
-    <n v="65696.97099999999"/>
+    <n v="65696.967000000004"/>
     <x v="0"/>
     <x v="0"/>
     <s v="A. CAPITAUX PROPRES"/>
@@ -3949,9 +3949,9 @@
     <s v="LUX"/>
     <n v="-683.76"/>
     <n v="0.17"/>
-    <n v="-116.23920000000001"/>
-    <n v="-799.99919999999997"/>
-    <n v="64896.971799999992"/>
+    <n v="-116.24"/>
+    <n v="-800"/>
+    <n v="64896.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -3976,9 +3976,9 @@
     <s v="LUX"/>
     <n v="-341.88"/>
     <n v="0.17"/>
-    <n v="-58.119600000000005"/>
-    <n v="-399.99959999999999"/>
-    <n v="64496.972199999989"/>
+    <n v="-58.12"/>
+    <n v="-400"/>
+    <n v="64496.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -4003,9 +4003,9 @@
     <s v="LUX"/>
     <n v="1025.6399999999999"/>
     <n v="0.17"/>
-    <n v="174.3588"/>
-    <n v="1199.9987999999998"/>
-    <n v="65696.97099999999"/>
+    <n v="174.36"/>
+    <n v="1200"/>
+    <n v="65696.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -4030,9 +4030,9 @@
     <s v="LUX"/>
     <n v="-1025.6399999999999"/>
     <n v="0.17"/>
-    <n v="-174.3588"/>
-    <n v="-1199.9987999999998"/>
-    <n v="64496.972199999989"/>
+    <n v="-174.36"/>
+    <n v="-1200"/>
+    <n v="64496.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -4059,7 +4059,7 @@
     <m/>
     <m/>
     <n v="-250"/>
-    <n v="64246.972199999989"/>
+    <n v="64246.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -4079,14 +4079,14 @@
     <n v="7"/>
     <x v="1"/>
     <n v="2026"/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="287356"/>
+    <n v="5.7471199999999998"/>
     <s v="LUX"/>
     <n v="-50000"/>
     <m/>
     <m/>
     <n v="-50000"/>
-    <n v="14246.972199999989"/>
+    <n v="14246.967000000004"/>
     <x v="0"/>
     <x v="2"/>
     <s v="23 - IMMOBILISATIONS FINANCIERES"/>
@@ -4113,7 +4113,7 @@
     <m/>
     <m/>
     <n v="-25"/>
-    <n v="14221.972199999989"/>
+    <n v="14221.967000000004"/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -4187,13 +4187,13 @@
     <m/>
     <x v="2"/>
     <m/>
-    <n v="1156585"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="14221.972199999989"/>
+    <n v="1443941"/>
+    <n v="6.0164208333333331"/>
+    <m/>
+    <n v="-240000"/>
+    <m/>
+    <m/>
+    <n v="14221.967000000004"/>
     <m/>
     <x v="2"/>
     <x v="3"/>
@@ -4912,7 +4912,7 @@
     <col min="9" max="9" width="22" style="15" customWidth="1"/>
     <col min="10" max="10" width="39.5703125" style="15" customWidth="1"/>
     <col min="11" max="11" width="29.42578125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" style="14" customWidth="1"/>
+    <col min="12" max="12" width="29.140625" style="14" customWidth="1"/>
     <col min="13" max="13" width="31" style="14" customWidth="1"/>
     <col min="14" max="14" width="11" style="61" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" style="14" customWidth="1"/>
@@ -5174,7 +5174,7 @@
         <v>194</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="M8" s="25" t="s">
         <v>51</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N14" s="58" t="s">
         <v>147</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N15" s="58" t="s">
         <v>142</v>
@@ -7101,7 +7101,7 @@
         <v>51</v>
       </c>
       <c r="N42" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O42" s="27">
         <v>-341.88</v>
@@ -7160,7 +7160,7 @@
         <v>51</v>
       </c>
       <c r="N43" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O43" s="27">
         <v>-341.88</v>
@@ -7219,7 +7219,7 @@
         <v>51</v>
       </c>
       <c r="N44" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O44" s="27">
         <v>-341.88</v>
@@ -7278,7 +7278,7 @@
         <v>51</v>
       </c>
       <c r="N45" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O45" s="27">
         <v>-341.88</v>
@@ -7337,7 +7337,7 @@
         <v>51</v>
       </c>
       <c r="N46" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O46" s="27">
         <v>-341.88</v>
@@ -7396,7 +7396,7 @@
         <v>51</v>
       </c>
       <c r="N47" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O47" s="27">
         <f>-341.88*2</f>
@@ -7456,7 +7456,7 @@
         <v>51</v>
       </c>
       <c r="N48" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O48" s="27">
         <v>-341.88</v>
@@ -7515,7 +7515,7 @@
         <v>51</v>
       </c>
       <c r="N49" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O49" s="27">
         <v>-341.88</v>
@@ -7574,7 +7574,7 @@
         <v>51</v>
       </c>
       <c r="N50" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O50" s="27">
         <v>-341.88</v>
@@ -7628,13 +7628,13 @@
         <v>-200000</v>
       </c>
       <c r="L51" s="34" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="M51" s="47" t="s">
         <v>51</v>
       </c>
       <c r="N51" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O51" s="27">
         <f>-SUM(O42:O50)</f>
@@ -7695,7 +7695,7 @@
         <v>203</v>
       </c>
       <c r="N52" s="58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O52" s="27">
         <f>-O51</f>
@@ -8135,10 +8135,10 @@
         <v>58</v>
       </c>
       <c r="K60" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L60" s="34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M60" s="25" t="s">
         <v>51</v>
@@ -8192,10 +8192,10 @@
         <v>58</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L61" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M61" s="25" t="s">
         <v>51</v>
@@ -8252,13 +8252,13 @@
         <v>40000</v>
       </c>
       <c r="L62" s="34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M62" s="47" t="s">
         <v>51</v>
       </c>
       <c r="N62" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O62" s="27">
         <v>-683.76</v>
@@ -8311,13 +8311,13 @@
         <v>20000</v>
       </c>
       <c r="L63" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M63" s="47" t="s">
         <v>51</v>
       </c>
       <c r="N63" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O63" s="27">
         <v>-341.88</v>
@@ -8371,13 +8371,13 @@
         <v>0</v>
       </c>
       <c r="L64" s="34" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="M64" s="47" t="s">
         <v>51</v>
       </c>
       <c r="N64" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O64" s="27">
         <f>-O62-O63</f>
@@ -8438,7 +8438,7 @@
         <v>203</v>
       </c>
       <c r="N65" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O65" s="27">
         <f>-O64</f>
@@ -9320,7 +9320,7 @@
         <v>42</v>
       </c>
       <c r="S6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T6" s="56" t="s">
         <v>71</v>
@@ -9458,13 +9458,13 @@
         <v>42</v>
       </c>
       <c r="S8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T8" s="56" t="s">
         <v>73</v>
       </c>
       <c r="U8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W8" t="s">
         <v>51</v>
@@ -9527,13 +9527,13 @@
         <v>42</v>
       </c>
       <c r="S9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T9" s="56" t="s">
         <v>74</v>
       </c>
       <c r="U9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W9" t="s">
         <v>51</v>
@@ -11225,16 +11225,15 @@
         <v>0.17</v>
       </c>
       <c r="K36" s="8">
-        <f>I36*J36</f>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L36" s="8">
         <f>I36+K36</f>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M36" s="8">
         <f t="shared" si="47"/>
-        <v>49573.517400000004</v>
+        <v>49573.517000000007</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>16</v>
@@ -11248,7 +11247,7 @@
         <v>186</v>
       </c>
       <c r="T36" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U36" t="s">
         <v>203</v>
@@ -11290,16 +11289,15 @@
         <v>0.17</v>
       </c>
       <c r="K37" s="8">
-        <f t="shared" ref="K37:K46" si="50">I37*J37</f>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L37" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M37" s="8">
         <f t="shared" si="47"/>
-        <v>49173.517800000001</v>
+        <v>49173.517000000007</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>16</v>
@@ -11313,7 +11311,7 @@
         <v>186</v>
       </c>
       <c r="T37" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U37" t="s">
         <v>203</v>
@@ -11355,16 +11353,15 @@
         <v>0.17</v>
       </c>
       <c r="K38" s="8">
-        <f t="shared" si="50"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L38" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M38" s="8">
         <f t="shared" si="47"/>
-        <v>48773.518199999999</v>
+        <v>48773.517000000007</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>16</v>
@@ -11378,7 +11375,7 @@
         <v>186</v>
       </c>
       <c r="T38" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U38" t="s">
         <v>203</v>
@@ -11420,16 +11417,15 @@
         <v>0.17</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="50"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L39" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M39" s="8">
         <f t="shared" si="47"/>
-        <v>48373.518599999996</v>
+        <v>48373.517000000007</v>
       </c>
       <c r="N39" s="9" t="s">
         <v>16</v>
@@ -11443,7 +11439,7 @@
         <v>186</v>
       </c>
       <c r="T39" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U39" t="s">
         <v>203</v>
@@ -11485,16 +11481,15 @@
         <v>0.17</v>
       </c>
       <c r="K40" s="8">
-        <f t="shared" si="50"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L40" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M40" s="8">
         <f t="shared" si="47"/>
-        <v>47973.518999999993</v>
+        <v>47973.517000000007</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>16</v>
@@ -11508,7 +11503,7 @@
         <v>186</v>
       </c>
       <c r="T40" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U40" t="s">
         <v>203</v>
@@ -11551,16 +11546,15 @@
         <v>0.17</v>
       </c>
       <c r="K41" s="8">
-        <f t="shared" si="50"/>
-        <v>-116.23920000000001</v>
+        <v>-116.24</v>
       </c>
       <c r="L41" s="8">
         <f t="shared" si="46"/>
-        <v>-799.99919999999997</v>
+        <v>-800</v>
       </c>
       <c r="M41" s="8">
         <f t="shared" si="47"/>
-        <v>47173.519799999995</v>
+        <v>47173.517000000007</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>16</v>
@@ -11574,7 +11568,7 @@
         <v>186</v>
       </c>
       <c r="T41" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U41" t="s">
         <v>203</v>
@@ -11616,16 +11610,15 @@
         <v>0.17</v>
       </c>
       <c r="K42" s="8">
-        <f t="shared" si="50"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L42" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M42" s="8">
         <f t="shared" si="47"/>
-        <v>46773.520199999992</v>
+        <v>46773.517000000007</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>16</v>
@@ -11639,7 +11632,7 @@
         <v>186</v>
       </c>
       <c r="T42" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U42" t="s">
         <v>203</v>
@@ -11681,16 +11674,15 @@
         <v>0.17</v>
       </c>
       <c r="K43" s="8">
-        <f t="shared" si="50"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L43" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M43" s="8">
         <f t="shared" si="47"/>
-        <v>46373.520599999989</v>
+        <v>46373.517000000007</v>
       </c>
       <c r="N43" s="9" t="s">
         <v>16</v>
@@ -11704,7 +11696,7 @@
         <v>186</v>
       </c>
       <c r="T43" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U43" t="s">
         <v>203</v>
@@ -11746,16 +11738,15 @@
         <v>0.17</v>
       </c>
       <c r="K44" s="8">
-        <f t="shared" si="50"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L44" s="8">
         <f t="shared" si="46"/>
-        <v>-399.99959999999999</v>
+        <v>-400</v>
       </c>
       <c r="M44" s="8">
         <f t="shared" si="47"/>
-        <v>45973.520999999986</v>
+        <v>45973.517000000007</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>16</v>
@@ -11769,7 +11760,7 @@
         <v>186</v>
       </c>
       <c r="T44" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U44" t="s">
         <v>203</v>
@@ -11812,16 +11803,15 @@
         <v>0.17</v>
       </c>
       <c r="K45" s="8">
-        <f t="shared" si="50"/>
-        <v>581.19600000000003</v>
+        <v>581.20000000000005</v>
       </c>
       <c r="L45" s="8">
         <f t="shared" si="46"/>
-        <v>3999.9960000000001</v>
+        <v>4000</v>
       </c>
       <c r="M45" s="8">
         <f t="shared" si="47"/>
-        <v>49973.516999999985</v>
+        <v>49973.517000000007</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>16</v>
@@ -11835,7 +11825,7 @@
         <v>186</v>
       </c>
       <c r="T45" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U45" t="s">
         <v>203</v>
@@ -11878,16 +11868,15 @@
         <v>0.17</v>
       </c>
       <c r="K46" s="8">
-        <f t="shared" si="50"/>
-        <v>-581.19600000000003</v>
+        <v>-581.20000000000005</v>
       </c>
       <c r="L46" s="8">
         <f t="shared" si="46"/>
-        <v>-3999.9960000000001</v>
+        <v>-4000</v>
       </c>
       <c r="M46" s="8">
         <f t="shared" si="47"/>
-        <v>45973.520999999986</v>
+        <v>45973.517000000007</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>16</v>
@@ -11901,7 +11890,7 @@
         <v>186</v>
       </c>
       <c r="T46" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U46" t="s">
         <v>203</v>
@@ -11940,12 +11929,12 @@
         <v>-250</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" ref="L47:L59" si="51">I47+K47</f>
+        <f t="shared" ref="L47:L59" si="50">I47+K47</f>
         <v>-250</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" ref="M47:M59" si="52">M46+L47</f>
-        <v>45723.520999999986</v>
+        <f t="shared" ref="M47:M59" si="51">M46+L47</f>
+        <v>45723.517000000007</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>16</v>
@@ -12002,16 +11991,16 @@
         <v>0.17</v>
       </c>
       <c r="K48" s="8">
-        <f t="shared" ref="K48" si="53">I48*J48</f>
+        <f t="shared" ref="K48" si="52">I48*J48</f>
         <v>-2.5500000000000003</v>
       </c>
       <c r="L48" s="8">
+        <f t="shared" si="50"/>
+        <v>-17.55</v>
+      </c>
+      <c r="M48" s="8">
         <f t="shared" si="51"/>
-        <v>-17.55</v>
-      </c>
-      <c r="M48" s="8">
-        <f t="shared" si="52"/>
-        <v>45705.970999999983</v>
+        <v>45705.967000000004</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>16</v>
@@ -12074,12 +12063,12 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="L49" s="8">
+        <f t="shared" si="50"/>
+        <v>17.55</v>
+      </c>
+      <c r="M49" s="8">
         <f t="shared" si="51"/>
-        <v>17.55</v>
-      </c>
-      <c r="M49" s="8">
-        <f t="shared" si="52"/>
-        <v>45723.520999999986</v>
+        <v>45723.517000000007</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>16</v>
@@ -12140,16 +12129,16 @@
         <v>0.17</v>
       </c>
       <c r="K50" s="8">
-        <f t="shared" ref="K50" si="54">-K49</f>
+        <f t="shared" ref="K50" si="53">-K49</f>
         <v>-2.5499999999999998</v>
       </c>
       <c r="L50" s="8">
+        <f t="shared" si="50"/>
+        <v>-17.55</v>
+      </c>
+      <c r="M50" s="8">
         <f t="shared" si="51"/>
-        <v>-17.55</v>
-      </c>
-      <c r="M50" s="8">
-        <f t="shared" si="52"/>
-        <v>45705.970999999983</v>
+        <v>45705.967000000004</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>16</v>
@@ -12211,12 +12200,12 @@
         <v>-40000</v>
       </c>
       <c r="L51" s="8">
+        <f t="shared" si="50"/>
+        <v>-40000</v>
+      </c>
+      <c r="M51" s="8">
         <f t="shared" si="51"/>
-        <v>-40000</v>
-      </c>
-      <c r="M51" s="8">
-        <f t="shared" si="52"/>
-        <v>5705.9709999999832</v>
+        <v>5705.9670000000042</v>
       </c>
       <c r="N51" s="66" t="s">
         <v>11</v>
@@ -12275,12 +12264,12 @@
         <v>-5</v>
       </c>
       <c r="L52" s="8">
+        <f t="shared" si="50"/>
+        <v>-5</v>
+      </c>
+      <c r="M52" s="8">
         <f t="shared" si="51"/>
-        <v>-5</v>
-      </c>
-      <c r="M52" s="8">
-        <f t="shared" si="52"/>
-        <v>5700.9709999999832</v>
+        <v>5700.9670000000042</v>
       </c>
       <c r="N52" s="9" t="s">
         <v>16</v>
@@ -12334,12 +12323,12 @@
         <v>-4</v>
       </c>
       <c r="L53" s="8">
+        <f t="shared" si="50"/>
+        <v>-4</v>
+      </c>
+      <c r="M53" s="8">
         <f t="shared" si="51"/>
-        <v>-4</v>
-      </c>
-      <c r="M53" s="8">
-        <f t="shared" si="52"/>
-        <v>5696.9709999999832</v>
+        <v>5696.9670000000042</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>16</v>
@@ -12392,12 +12381,12 @@
         <v>40000</v>
       </c>
       <c r="L54" s="8">
+        <f t="shared" si="50"/>
+        <v>40000</v>
+      </c>
+      <c r="M54" s="8">
         <f t="shared" si="51"/>
-        <v>40000</v>
-      </c>
-      <c r="M54" s="8">
-        <f t="shared" si="52"/>
-        <v>45696.970999999983</v>
+        <v>45696.967000000004</v>
       </c>
       <c r="N54" s="9" t="s">
         <v>11</v>
@@ -12415,13 +12404,13 @@
         <v>47</v>
       </c>
       <c r="U54" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V54" t="s">
         <v>82</v>
       </c>
       <c r="W54" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X54" s="9" t="s">
         <v>88</v>
@@ -12453,12 +12442,12 @@
         <v>20000</v>
       </c>
       <c r="L55" s="8">
+        <f t="shared" si="50"/>
+        <v>20000</v>
+      </c>
+      <c r="M55" s="8">
         <f t="shared" si="51"/>
-        <v>20000</v>
-      </c>
-      <c r="M55" s="8">
-        <f t="shared" si="52"/>
-        <v>65696.97099999999</v>
+        <v>65696.967000000004</v>
       </c>
       <c r="N55" s="9" t="s">
         <v>11</v>
@@ -12476,13 +12465,13 @@
         <v>47</v>
       </c>
       <c r="U55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="V55" t="s">
         <v>82</v>
       </c>
       <c r="W55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X55" s="9" t="s">
         <v>88</v>
@@ -12496,11 +12485,11 @@
         <v>46220</v>
       </c>
       <c r="C56" s="7">
-        <f t="shared" ref="C56:C62" si="55">IF(B56="","",MONTH(B56))</f>
+        <f t="shared" ref="C56:C62" si="54">IF(B56="","",MONTH(B56))</f>
         <v>7</v>
       </c>
       <c r="D56" s="7">
-        <f t="shared" ref="D56:D62" si="56">IF(B56="","",YEAR(B56))</f>
+        <f t="shared" ref="D56:D62" si="55">IF(B56="","",YEAR(B56))</f>
         <v>2026</v>
       </c>
       <c r="E56" s="7">
@@ -12518,16 +12507,15 @@
         <v>0.17</v>
       </c>
       <c r="K56" s="8">
-        <f t="shared" ref="K56:K59" si="57">I56*J56</f>
-        <v>-116.23920000000001</v>
+        <v>-116.24</v>
       </c>
       <c r="L56" s="8">
+        <f t="shared" si="50"/>
+        <v>-800</v>
+      </c>
+      <c r="M56" s="8">
         <f t="shared" si="51"/>
-        <v>-799.99919999999997</v>
-      </c>
-      <c r="M56" s="8">
-        <f t="shared" si="52"/>
-        <v>64896.971799999992</v>
+        <v>64896.967000000004</v>
       </c>
       <c r="N56" s="9" t="s">
         <v>16</v>
@@ -12541,13 +12529,13 @@
         <v>186</v>
       </c>
       <c r="T56" s="56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U56" t="s">
         <v>203</v>
       </c>
       <c r="W56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X56" s="9" t="s">
         <v>88</v>
@@ -12561,11 +12549,11 @@
         <v>46220</v>
       </c>
       <c r="C57" s="7">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D57" s="7">
         <f t="shared" si="55"/>
-        <v>7</v>
-      </c>
-      <c r="D57" s="7">
-        <f t="shared" si="56"/>
         <v>2026</v>
       </c>
       <c r="E57" s="7">
@@ -12583,16 +12571,15 @@
         <v>0.17</v>
       </c>
       <c r="K57" s="8">
-        <f t="shared" si="57"/>
-        <v>-58.119600000000005</v>
+        <v>-58.12</v>
       </c>
       <c r="L57" s="8">
+        <f t="shared" si="50"/>
+        <v>-400</v>
+      </c>
+      <c r="M57" s="8">
         <f t="shared" si="51"/>
-        <v>-399.99959999999999</v>
-      </c>
-      <c r="M57" s="8">
-        <f t="shared" si="52"/>
-        <v>64496.972199999989</v>
+        <v>64496.967000000004</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>16</v>
@@ -12606,13 +12593,13 @@
         <v>186</v>
       </c>
       <c r="T57" s="56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U57" t="s">
         <v>203</v>
       </c>
       <c r="W57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X57" s="9" t="s">
         <v>88</v>
@@ -12626,11 +12613,11 @@
         <v>46220</v>
       </c>
       <c r="C58" s="7">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D58" s="7">
         <f t="shared" si="55"/>
-        <v>7</v>
-      </c>
-      <c r="D58" s="7">
-        <f t="shared" si="56"/>
         <v>2026</v>
       </c>
       <c r="E58" s="7">
@@ -12649,16 +12636,15 @@
         <v>0.17</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="57"/>
-        <v>174.3588</v>
+        <v>174.36</v>
       </c>
       <c r="L58" s="8">
+        <f t="shared" si="50"/>
+        <v>1200</v>
+      </c>
+      <c r="M58" s="8">
         <f t="shared" si="51"/>
-        <v>1199.9987999999998</v>
-      </c>
-      <c r="M58" s="8">
-        <f t="shared" si="52"/>
-        <v>65696.97099999999</v>
+        <v>65696.967000000004</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>16</v>
@@ -12672,7 +12658,7 @@
         <v>186</v>
       </c>
       <c r="T58" s="56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U58" t="s">
         <v>203</v>
@@ -12692,11 +12678,11 @@
         <v>46220</v>
       </c>
       <c r="C59" s="7">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D59" s="7">
         <f t="shared" si="55"/>
-        <v>7</v>
-      </c>
-      <c r="D59" s="7">
-        <f t="shared" si="56"/>
         <v>2026</v>
       </c>
       <c r="E59" s="7">
@@ -12715,16 +12701,15 @@
         <v>0.17</v>
       </c>
       <c r="K59" s="8">
-        <f t="shared" si="57"/>
-        <v>-174.3588</v>
+        <v>-174.36</v>
       </c>
       <c r="L59" s="8">
+        <f t="shared" si="50"/>
+        <v>-1200</v>
+      </c>
+      <c r="M59" s="8">
         <f t="shared" si="51"/>
-        <v>-1199.9987999999998</v>
-      </c>
-      <c r="M59" s="8">
-        <f t="shared" si="52"/>
-        <v>64496.972199999989</v>
+        <v>64496.967000000004</v>
       </c>
       <c r="N59" s="9" t="s">
         <v>16</v>
@@ -12738,7 +12723,7 @@
         <v>186</v>
       </c>
       <c r="T59" s="56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U59" t="s">
         <v>203</v>
@@ -12758,11 +12743,11 @@
         <v>46224</v>
       </c>
       <c r="C60" s="7">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D60" s="7">
         <f t="shared" si="55"/>
-        <v>7</v>
-      </c>
-      <c r="D60" s="7">
-        <f t="shared" si="56"/>
         <v>2026</v>
       </c>
       <c r="E60" s="7">
@@ -12777,12 +12762,12 @@
         <v>-250</v>
       </c>
       <c r="L60" s="8">
-        <f t="shared" ref="L60:L62" si="58">I60+K60</f>
+        <f t="shared" ref="L60:L62" si="56">I60+K60</f>
         <v>-250</v>
       </c>
       <c r="M60" s="8">
-        <f t="shared" ref="M60:M62" si="59">M59+L60</f>
-        <v>64246.972199999989</v>
+        <f t="shared" ref="M60:M62" si="57">M59+L60</f>
+        <v>64246.967000000004</v>
       </c>
       <c r="N60" s="9" t="s">
         <v>16</v>
@@ -12817,11 +12802,11 @@
         <v>46230</v>
       </c>
       <c r="C61" s="7">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D61" s="7">
         <f t="shared" si="55"/>
-        <v>7</v>
-      </c>
-      <c r="D61" s="7">
-        <f t="shared" si="56"/>
         <v>2026</v>
       </c>
       <c r="E61" s="7">
@@ -12841,12 +12826,12 @@
         <v>-50000</v>
       </c>
       <c r="L61" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-50000</v>
       </c>
       <c r="M61" s="8">
-        <f t="shared" si="59"/>
-        <v>14246.972199999989</v>
+        <f t="shared" si="57"/>
+        <v>14246.967000000004</v>
       </c>
       <c r="N61" s="66" t="s">
         <v>11</v>
@@ -12886,11 +12871,11 @@
         <v>46230</v>
       </c>
       <c r="C62" s="7">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D62" s="7">
         <f t="shared" si="55"/>
-        <v>7</v>
-      </c>
-      <c r="D62" s="7">
-        <f t="shared" si="56"/>
         <v>2026</v>
       </c>
       <c r="E62" s="7">
@@ -12905,12 +12890,12 @@
         <v>-25</v>
       </c>
       <c r="L62" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-25</v>
       </c>
       <c r="M62" s="8">
-        <f t="shared" si="59"/>
-        <v>14221.972199999989</v>
+        <f t="shared" si="57"/>
+        <v>14221.967000000004</v>
       </c>
       <c r="N62" s="9" t="s">
         <v>16</v>
@@ -12966,7 +12951,7 @@
       </c>
       <c r="L65" s="45">
         <f>SUBTOTAL(9,L2:L64)</f>
-        <v>14221.972199999989</v>
+        <v>14221.967000000004</v>
       </c>
     </row>
     <row r="66" spans="3:25">
@@ -12977,11 +12962,11 @@
     </row>
     <row r="68" spans="3:25">
       <c r="C68" s="7" t="str">
-        <f t="shared" ref="C68:C70" si="60">IF(B68="","",MONTH(B68))</f>
+        <f t="shared" ref="C68:C70" si="58">IF(B68="","",MONTH(B68))</f>
         <v/>
       </c>
       <c r="D68" s="7" t="str">
-        <f t="shared" ref="D68:D70" si="61">IF(B68="","",YEAR(B68))</f>
+        <f t="shared" ref="D68:D70" si="59">IF(B68="","",YEAR(B68))</f>
         <v/>
       </c>
       <c r="F68" s="46"/>
@@ -12996,15 +12981,15 @@
         <v>0.17</v>
       </c>
       <c r="K68" s="8">
-        <f t="shared" ref="K68:K69" si="62">I68*J68</f>
+        <f t="shared" ref="K68:K69" si="60">I68*J68</f>
         <v>0</v>
       </c>
       <c r="L68" s="8">
-        <f t="shared" ref="L68:L70" si="63">I68+K68</f>
+        <f t="shared" ref="L68:L70" si="61">I68+K68</f>
         <v>0</v>
       </c>
       <c r="M68" s="8">
-        <f t="shared" ref="M68:M70" si="64">M67+L68</f>
+        <f t="shared" ref="M68:M70" si="62">M67+L68</f>
         <v>0</v>
       </c>
       <c r="N68" s="9" t="s">
@@ -13037,11 +13022,11 @@
     </row>
     <row r="69" spans="3:25">
       <c r="C69" s="7" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="D69" s="7" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="F69" s="46"/>
@@ -13056,17 +13041,17 @@
         <v>0.17</v>
       </c>
       <c r="K69" s="8">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="8">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="8">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="L69" s="8">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="8">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
       <c r="N69" s="9" t="s">
         <v>16</v>
       </c>
@@ -13097,11 +13082,11 @@
     </row>
     <row r="70" spans="3:25">
       <c r="C70" s="7" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="D70" s="7" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="F70" s="46"/>
@@ -13117,15 +13102,15 @@
         <v>0.17</v>
       </c>
       <c r="K70" s="8">
-        <f t="shared" ref="K70" si="65">-K69</f>
+        <f t="shared" ref="K70" si="63">-K69</f>
         <v>0</v>
       </c>
       <c r="L70" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M70" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="N70" s="9" t="s">
@@ -13425,7 +13410,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -13445,7 +13430,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -13623,7 +13608,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B47" s="8">
         <v>-25.0731</v>
@@ -13657,7 +13642,7 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -13665,7 +13650,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="82" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B51" s="8">
         <v>-100</v>
@@ -13697,10 +13682,10 @@
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8">
-        <v>-5199.9948000000004</v>
+        <v>-5200</v>
       </c>
       <c r="D54" s="8">
-        <v>-5199.9948000000004</v>
+        <v>-5200</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -13711,10 +13696,10 @@
         <v>50223.517</v>
       </c>
       <c r="C55" s="8">
-        <v>-36001.544800000003</v>
+        <v>-36001.550000000003</v>
       </c>
       <c r="D55" s="8">
-        <v>14221.972199999997</v>
+        <v>14221.966999999997</v>
       </c>
     </row>
   </sheetData>
@@ -14485,7 +14470,7 @@
         <v>2</v>
       </c>
       <c r="B38" s="179" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C38" s="74" t="s">
         <v>100</v>
@@ -14692,7 +14677,7 @@
         <v>132</v>
       </c>
       <c r="G49" s="85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H49" s="85" t="s">
         <v>131</v>
@@ -15631,7 +15616,7 @@
         <v>163</v>
       </c>
       <c r="L15" s="123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M15" s="123" t="s">
         <v>35</v>
@@ -15685,7 +15670,7 @@
         <v>Edoardo TUBIA</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K18" s="6">
         <v>46048</v>
@@ -15716,7 +15701,7 @@
       <c r="G19" s="137"/>
       <c r="H19" s="76"/>
       <c r="J19" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K19" s="6">
         <v>46048</v>
@@ -15750,7 +15735,7 @@
       </c>
       <c r="H20" s="76"/>
       <c r="J20" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K20" s="6">
         <v>46048</v>
@@ -15807,7 +15792,7 @@
         <v>Silvia TUBIA</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K22" s="6">
         <v>46048</v>
@@ -15863,7 +15848,7 @@
         <v>Stefano BERTOZZI</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K24" s="6">
         <v>46048</v>
@@ -15919,7 +15904,7 @@
         <v>Maria DE MIGUEL BELLVIS</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K26" s="6">
         <v>46048</v>
@@ -15975,7 +15960,7 @@
         <v>Salvatore DESIDERIO</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K28" s="6">
         <v>46048</v>
@@ -16031,7 +16016,7 @@
         <v>Enrico TUBIA</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K30" s="6">
         <v>46048</v>
@@ -16087,7 +16072,7 @@
         <v>Greta ZANIBONI</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K32" s="6">
         <v>46048</v>
@@ -16143,7 +16128,7 @@
         <v>Elisa ZANIBONI</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K34" s="6">
         <v>46048</v>
@@ -16178,7 +16163,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="134" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D36" s="135">
         <v>40000</v>
@@ -16199,7 +16184,7 @@
         <v>Marco STERZI</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K36" s="6">
         <v>46220</v>
@@ -16234,7 +16219,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="134" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D38" s="135">
         <v>20000</v>
@@ -16255,7 +16240,7 @@
         <v>Giovanni MILETTI</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K38" s="6">
         <v>46220</v>

--- a/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
+++ b/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GREEN ENERBRAS ONE SCSp\GREEN ENERBRAS ONE SCSp\BILAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443AC865-550A-40D5-BAD4-7BF25EE532CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A640EC-5DD9-4561-AD94-4E5CF0EE7ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,7 +779,7 @@
     <t>Cambio medio</t>
   </si>
   <si>
-    <t>New Life Sarl (General Partner)</t>
+    <t>New Life Sarl</t>
   </si>
 </sst>
 </file>
